--- a/data/all_cities_blddensity.xlsx
+++ b/data/all_cities_blddensity.xlsx
@@ -1,15 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView windowWidth="18350" windowHeight="6880"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -22,222 +35,570 @@
     <t>mean_blddensity</t>
   </si>
   <si>
-    <t>三亚.xlsx</t>
-  </si>
-  <si>
-    <t>上海.xlsx</t>
-  </si>
-  <si>
-    <t>东莞.xlsx</t>
-  </si>
-  <si>
-    <t>中山.xlsx</t>
-  </si>
-  <si>
-    <t>佛山.xlsx</t>
-  </si>
-  <si>
-    <t>保定.xlsx</t>
-  </si>
-  <si>
-    <t>兰州.xlsx</t>
-  </si>
-  <si>
-    <t>北京.xlsx</t>
-  </si>
-  <si>
-    <t>南京.xlsx</t>
-  </si>
-  <si>
-    <t>南宁.xlsx</t>
-  </si>
-  <si>
-    <t>南昌.xlsx</t>
-  </si>
-  <si>
-    <t>南通.xlsx</t>
-  </si>
-  <si>
-    <t>厦门.xlsx</t>
-  </si>
-  <si>
-    <t>台州.xlsx</t>
-  </si>
-  <si>
-    <t>合肥.xlsx</t>
-  </si>
-  <si>
-    <t>呼和浩特.xlsx</t>
-  </si>
-  <si>
-    <t>哈尔滨.xlsx</t>
-  </si>
-  <si>
-    <t>唐山.xlsx</t>
-  </si>
-  <si>
-    <t>嘉兴.xlsx</t>
-  </si>
-  <si>
-    <t>大连.xlsx</t>
-  </si>
-  <si>
-    <t>天津.xlsx</t>
-  </si>
-  <si>
-    <t>太原.xlsx</t>
-  </si>
-  <si>
-    <t>宁波.xlsx</t>
-  </si>
-  <si>
-    <t>常州.xlsx</t>
-  </si>
-  <si>
-    <t>广州.xlsx</t>
-  </si>
-  <si>
-    <t>徐州.xlsx</t>
-  </si>
-  <si>
-    <t>惠州.xlsx</t>
-  </si>
-  <si>
-    <t>成都.xlsx</t>
-  </si>
-  <si>
-    <t>扬州.xlsx</t>
-  </si>
-  <si>
-    <t>拉萨.xlsx</t>
-  </si>
-  <si>
-    <t>无锡.xlsx</t>
-  </si>
-  <si>
-    <t>昆明.xlsx</t>
-  </si>
-  <si>
-    <t>杭州.xlsx</t>
-  </si>
-  <si>
-    <t>武汉.xlsx</t>
-  </si>
-  <si>
-    <t>汕头.xlsx</t>
-  </si>
-  <si>
-    <t>沈阳.xlsx</t>
-  </si>
-  <si>
-    <t>泉州.xlsx</t>
-  </si>
-  <si>
-    <t>洛阳.xlsx</t>
-  </si>
-  <si>
-    <t>济南.xlsx</t>
-  </si>
-  <si>
-    <t>海口.xlsx</t>
-  </si>
-  <si>
-    <t>深圳.xlsx</t>
-  </si>
-  <si>
-    <t>温州.xlsx</t>
-  </si>
-  <si>
-    <t>澳门.xlsx</t>
-  </si>
-  <si>
-    <t>烟台.xlsx</t>
-  </si>
-  <si>
-    <t>珠海.xlsx</t>
-  </si>
-  <si>
-    <t>石家庄.xlsx</t>
-  </si>
-  <si>
-    <t>福州.xlsx</t>
-  </si>
-  <si>
-    <t>绍兴.xlsx</t>
-  </si>
-  <si>
-    <t>芜湖.xlsx</t>
-  </si>
-  <si>
-    <t>苏州.xlsx</t>
-  </si>
-  <si>
-    <t>西宁.xlsx</t>
-  </si>
-  <si>
-    <t>西安.xlsx</t>
-  </si>
-  <si>
-    <t>贵阳.xlsx</t>
-  </si>
-  <si>
-    <t>郑州.xlsx</t>
-  </si>
-  <si>
-    <t>鄂尔多斯.xlsx</t>
-  </si>
-  <si>
-    <t>重庆.xlsx</t>
-  </si>
-  <si>
-    <t>金华.xlsx</t>
-  </si>
-  <si>
-    <t>银川.xlsx</t>
-  </si>
-  <si>
-    <t>长春.xlsx</t>
-  </si>
-  <si>
-    <t>长沙.xlsx</t>
-  </si>
-  <si>
-    <t>青岛.xlsx</t>
-  </si>
-  <si>
-    <t>香港.xlsx</t>
+    <t>Sanya</t>
+  </si>
+  <si>
+    <t>Shanghai</t>
+  </si>
+  <si>
+    <t>Dongguan</t>
+  </si>
+  <si>
+    <t>Zhongshan</t>
+  </si>
+  <si>
+    <t>Foshan</t>
+  </si>
+  <si>
+    <t>Baoding</t>
+  </si>
+  <si>
+    <t>Lanzhou</t>
+  </si>
+  <si>
+    <t>Beijing</t>
+  </si>
+  <si>
+    <t>Nanjing</t>
+  </si>
+  <si>
+    <t>Nanning</t>
+  </si>
+  <si>
+    <t>Nanchang</t>
+  </si>
+  <si>
+    <t>Nantong</t>
+  </si>
+  <si>
+    <t>Xiamen</t>
+  </si>
+  <si>
+    <t>Taizhou</t>
+  </si>
+  <si>
+    <t>Hefei</t>
+  </si>
+  <si>
+    <t>Hohhot</t>
+  </si>
+  <si>
+    <t>Harbin</t>
+  </si>
+  <si>
+    <t>Tangshan</t>
+  </si>
+  <si>
+    <t>Jiaxing</t>
+  </si>
+  <si>
+    <t>Dalian</t>
+  </si>
+  <si>
+    <t>Tianjin</t>
+  </si>
+  <si>
+    <t>Taiyuan</t>
+  </si>
+  <si>
+    <t>Ningbo</t>
+  </si>
+  <si>
+    <t>Changzhou</t>
+  </si>
+  <si>
+    <t>Guangzhou</t>
+  </si>
+  <si>
+    <t>Xuzhou</t>
+  </si>
+  <si>
+    <t>Huizhou</t>
+  </si>
+  <si>
+    <t>Chengdu</t>
+  </si>
+  <si>
+    <t>Yangzhou</t>
+  </si>
+  <si>
+    <t>Lhasa</t>
+  </si>
+  <si>
+    <t>Wuxi</t>
+  </si>
+  <si>
+    <t>Kunming</t>
+  </si>
+  <si>
+    <t>Hangzhou</t>
+  </si>
+  <si>
+    <t>Wuhan</t>
+  </si>
+  <si>
+    <t>Shantou</t>
+  </si>
+  <si>
+    <t>Shenyang</t>
+  </si>
+  <si>
+    <t>Quanzhou</t>
+  </si>
+  <si>
+    <t>Luoyang</t>
+  </si>
+  <si>
+    <t>Jinan</t>
+  </si>
+  <si>
+    <t>Haikou</t>
+  </si>
+  <si>
+    <t>Shenzhen</t>
+  </si>
+  <si>
+    <t>Wenzhou</t>
+  </si>
+  <si>
+    <t>Macao</t>
+  </si>
+  <si>
+    <t>Yantai</t>
+  </si>
+  <si>
+    <t>Zhuhai</t>
+  </si>
+  <si>
+    <t>Shijiazhaung</t>
+  </si>
+  <si>
+    <t>Fuzhou</t>
+  </si>
+  <si>
+    <t>Shaoxing</t>
+  </si>
+  <si>
+    <t>Wuhu</t>
+  </si>
+  <si>
+    <t>Suzhou</t>
+  </si>
+  <si>
+    <t>Xining</t>
+  </si>
+  <si>
+    <t>Xi'an</t>
+  </si>
+  <si>
+    <t>Guiyang</t>
+  </si>
+  <si>
+    <t>Zhengzhou</t>
+  </si>
+  <si>
+    <t>Ordos</t>
+  </si>
+  <si>
+    <t>Chongqing</t>
+  </si>
+  <si>
+    <t>Jinhua</t>
+  </si>
+  <si>
+    <t>Yinchuan</t>
+  </si>
+  <si>
+    <t>Changchun</t>
+  </si>
+  <si>
+    <t>Changsha</t>
+  </si>
+  <si>
+    <t>Qingdao</t>
+  </si>
+  <si>
+    <t>Hong Kong</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -260,21 +621,317 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -557,520 +1214,526 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:B63"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="1"/>
+  <cols>
+    <col min="1" max="1" width="9" style="1"/>
+    <col min="2" max="2" width="12.8181818181818" style="1"/>
+    <col min="3" max="16384" width="9" style="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" t="s">
+      <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B2">
-        <v>0.1031349022686481</v>
+      <c r="B2" s="1">
+        <v>0.103134902268648</v>
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" t="s">
+      <c r="A3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="1">
         <v>0.149912612948308</v>
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" t="s">
+      <c r="A4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B4">
-        <v>0.1421536239072519</v>
+      <c r="B4" s="1">
+        <v>0.142153623907252</v>
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" t="s">
+      <c r="A5" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="1">
         <v>0.15255952425715</v>
       </c>
     </row>
     <row r="6" spans="1:2">
-      <c r="A6" t="s">
+      <c r="A6" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B6">
-        <v>0.1690761053028169</v>
+      <c r="B6" s="1">
+        <v>0.169076105302817</v>
       </c>
     </row>
     <row r="7" spans="1:2">
-      <c r="A7" t="s">
+      <c r="A7" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B7">
-        <v>0.1955044239561642</v>
+      <c r="B7" s="1">
+        <v>0.195504423956164</v>
       </c>
     </row>
     <row r="8" spans="1:2">
-      <c r="A8" t="s">
+      <c r="A8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B8">
-        <v>0.2036856213225084</v>
+      <c r="B8" s="1">
+        <v>0.203685621322508</v>
       </c>
     </row>
     <row r="9" spans="1:2">
-      <c r="A9" t="s">
+      <c r="A9" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B9">
-        <v>0.1801489246328694</v>
+      <c r="B9" s="1">
+        <v>0.180148924632869</v>
       </c>
     </row>
     <row r="10" spans="1:2">
-      <c r="A10" t="s">
+      <c r="A10" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B10">
-        <v>0.1340174926482594</v>
+      <c r="B10" s="1">
+        <v>0.134017492648259</v>
       </c>
     </row>
     <row r="11" spans="1:2">
-      <c r="A11" t="s">
+      <c r="A11" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B11">
-        <v>0.1507143931017375</v>
+      <c r="B11" s="1">
+        <v>0.150714393101738</v>
       </c>
     </row>
     <row r="12" spans="1:2">
-      <c r="A12" t="s">
+      <c r="A12" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B12">
-        <v>0.1443208626618511</v>
+      <c r="B12" s="1">
+        <v>0.144320862661851</v>
       </c>
     </row>
     <row r="13" spans="1:2">
-      <c r="A13" t="s">
+      <c r="A13" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B13">
-        <v>0.1211792512697244</v>
+      <c r="B13" s="1">
+        <v>0.121179251269724</v>
       </c>
     </row>
     <row r="14" spans="1:2">
-      <c r="A14" t="s">
+      <c r="A14" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B14">
-        <v>0.1527762862919705</v>
+      <c r="B14" s="1">
+        <v>0.15277628629197</v>
       </c>
     </row>
     <row r="15" spans="1:2">
-      <c r="A15" t="s">
+      <c r="A15" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B15">
+      <c r="B15" s="1">
         <v>0.141147535772772</v>
       </c>
     </row>
     <row r="16" spans="1:2">
-      <c r="A16" t="s">
+      <c r="A16" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B16">
-        <v>0.1311779717555043</v>
+      <c r="B16" s="1">
+        <v>0.131177971755504</v>
       </c>
     </row>
     <row r="17" spans="1:2">
-      <c r="A17" t="s">
+      <c r="A17" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B17">
-        <v>0.2007892135539339</v>
+      <c r="B17" s="1">
+        <v>0.200789213553934</v>
       </c>
     </row>
     <row r="18" spans="1:2">
-      <c r="A18" t="s">
+      <c r="A18" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B18">
+      <c r="B18" s="1">
         <v>0.163494224741646</v>
       </c>
     </row>
     <row r="19" spans="1:2">
-      <c r="A19" t="s">
+      <c r="A19" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B19">
-        <v>0.1757030211626849</v>
+      <c r="B19" s="1">
+        <v>0.175703021162685</v>
       </c>
     </row>
     <row r="20" spans="1:2">
-      <c r="A20" t="s">
+      <c r="A20" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B20">
+      <c r="B20" s="1">
         <v>0.126797292948417</v>
       </c>
     </row>
     <row r="21" spans="1:2">
-      <c r="A21" t="s">
+      <c r="A21" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B21">
-        <v>0.1247676017413656</v>
+      <c r="B21" s="1">
+        <v>0.124767601741366</v>
       </c>
     </row>
     <row r="22" spans="1:2">
-      <c r="A22" t="s">
+      <c r="A22" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B22">
-        <v>0.1763659576524277</v>
+      <c r="B22" s="1">
+        <v>0.176365957652428</v>
       </c>
     </row>
     <row r="23" spans="1:2">
-      <c r="A23" t="s">
+      <c r="A23" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B23">
-        <v>0.1840385640278841</v>
+      <c r="B23" s="1">
+        <v>0.184038564027884</v>
       </c>
     </row>
     <row r="24" spans="1:2">
-      <c r="A24" t="s">
+      <c r="A24" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B24">
-        <v>0.1150268865096283</v>
+      <c r="B24" s="1">
+        <v>0.115026886509628</v>
       </c>
     </row>
     <row r="25" spans="1:2">
-      <c r="A25" t="s">
+      <c r="A25" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B25">
-        <v>0.1194134091510791</v>
+      <c r="B25" s="1">
+        <v>0.119413409151079</v>
       </c>
     </row>
     <row r="26" spans="1:2">
-      <c r="A26" t="s">
+      <c r="A26" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B26">
-        <v>0.1935242645682974</v>
+      <c r="B26" s="1">
+        <v>0.193524264568297</v>
       </c>
     </row>
     <row r="27" spans="1:2">
-      <c r="A27" t="s">
+      <c r="A27" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B27">
-        <v>0.1188671333484011</v>
+      <c r="B27" s="1">
+        <v>0.118867133348401</v>
       </c>
     </row>
     <row r="28" spans="1:2">
-      <c r="A28" t="s">
+      <c r="A28" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B28">
-        <v>0.1131683347098853</v>
+      <c r="B28" s="1">
+        <v>0.113168334709885</v>
       </c>
     </row>
     <row r="29" spans="1:2">
-      <c r="A29" t="s">
+      <c r="A29" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B29">
-        <v>0.1268286137549804</v>
+      <c r="B29" s="1">
+        <v>0.12682861375498</v>
       </c>
     </row>
     <row r="30" spans="1:2">
-      <c r="A30" t="s">
+      <c r="A30" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B30">
-        <v>0.1925523179437382</v>
+      <c r="B30" s="1">
+        <v>0.192552317943738</v>
       </c>
     </row>
     <row r="31" spans="1:2">
-      <c r="A31" t="s">
+      <c r="A31" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B31">
-        <v>0.1747050423485537</v>
+      <c r="B31" s="1">
+        <v>0.174705042348554</v>
       </c>
     </row>
     <row r="32" spans="1:2">
-      <c r="A32" t="s">
+      <c r="A32" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B32">
-        <v>0.1278598229594219</v>
+      <c r="B32" s="1">
+        <v>0.127859822959422</v>
       </c>
     </row>
     <row r="33" spans="1:2">
-      <c r="A33" t="s">
+      <c r="A33" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B33">
+      <c r="B33" s="1">
         <v>0.103586188913004</v>
       </c>
     </row>
     <row r="34" spans="1:2">
-      <c r="A34" t="s">
+      <c r="A34" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B34">
-        <v>0.1206623129431427</v>
+      <c r="B34" s="1">
+        <v>0.120662312943143</v>
       </c>
     </row>
     <row r="35" spans="1:2">
-      <c r="A35" t="s">
+      <c r="A35" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B35">
-        <v>0.1312208987295627</v>
+      <c r="B35" s="1">
+        <v>0.131220898729563</v>
       </c>
     </row>
     <row r="36" spans="1:2">
-      <c r="A36" t="s">
+      <c r="A36" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B36">
-        <v>0.2220852323120735</v>
+      <c r="B36" s="1">
+        <v>0.222085232312073</v>
       </c>
     </row>
     <row r="37" spans="1:2">
-      <c r="A37" t="s">
+      <c r="A37" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B37">
-        <v>0.1493654481871796</v>
+      <c r="B37" s="1">
+        <v>0.14936544818718</v>
       </c>
     </row>
     <row r="38" spans="1:2">
-      <c r="A38" t="s">
+      <c r="A38" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B38">
-        <v>0.1569177205991847</v>
+      <c r="B38" s="1">
+        <v>0.156917720599185</v>
       </c>
     </row>
     <row r="39" spans="1:2">
-      <c r="A39" t="s">
+      <c r="A39" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B39">
-        <v>0.1237203189945322</v>
+      <c r="B39" s="1">
+        <v>0.123720318994532</v>
       </c>
     </row>
     <row r="40" spans="1:2">
-      <c r="A40" t="s">
+      <c r="A40" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B40">
-        <v>0.1674337095718036</v>
+      <c r="B40" s="1">
+        <v>0.167433709571804</v>
       </c>
     </row>
     <row r="41" spans="1:2">
-      <c r="A41" t="s">
+      <c r="A41" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B41">
-        <v>0.1725489510645886</v>
+      <c r="B41" s="1">
+        <v>0.172548951064589</v>
       </c>
     </row>
     <row r="42" spans="1:2">
-      <c r="A42" t="s">
+      <c r="A42" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B42">
-        <v>0.1309000412342689</v>
+      <c r="B42" s="1">
+        <v>0.130900041234269</v>
       </c>
     </row>
     <row r="43" spans="1:2">
-      <c r="A43" t="s">
+      <c r="A43" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B43">
-        <v>0.1635214127773462</v>
+      <c r="B43" s="1">
+        <v>0.163521412777346</v>
       </c>
     </row>
     <row r="44" spans="1:2">
-      <c r="A44" t="s">
+      <c r="A44" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B44">
-        <v>0.1399529564380646</v>
+      <c r="B44" s="1">
+        <v>0.139952956438065</v>
       </c>
     </row>
     <row r="45" spans="1:2">
-      <c r="A45" t="s">
+      <c r="A45" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B45">
+      <c r="B45" s="1">
         <v>0.156069859238848</v>
       </c>
     </row>
     <row r="46" spans="1:2">
-      <c r="A46" t="s">
+      <c r="A46" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B46">
+      <c r="B46" s="1">
         <v>0.152320532257309</v>
       </c>
     </row>
     <row r="47" spans="1:2">
-      <c r="A47" t="s">
+      <c r="A47" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="B47">
-        <v>0.1495825037256711</v>
+      <c r="B47" s="1">
+        <v>0.149582503725671</v>
       </c>
     </row>
     <row r="48" spans="1:2">
-      <c r="A48" t="s">
+      <c r="A48" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B48">
-        <v>0.1547366149049807</v>
+      <c r="B48" s="1">
+        <v>0.154736614904981</v>
       </c>
     </row>
     <row r="49" spans="1:2">
-      <c r="A49" t="s">
+      <c r="A49" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B49">
-        <v>0.1130346338109424</v>
+      <c r="B49" s="1">
+        <v>0.113034633810942</v>
       </c>
     </row>
     <row r="50" spans="1:2">
-      <c r="A50" t="s">
+      <c r="A50" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B50">
-        <v>0.1415350880696733</v>
+      <c r="B50" s="1">
+        <v>0.141535088069673</v>
       </c>
     </row>
     <row r="51" spans="1:2">
-      <c r="A51" t="s">
+      <c r="A51" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B51">
-        <v>0.1507111736055878</v>
+      <c r="B51" s="1">
+        <v>0.150711173605588</v>
       </c>
     </row>
     <row r="52" spans="1:2">
-      <c r="A52" t="s">
+      <c r="A52" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="B52">
-        <v>0.1587043732611669</v>
+      <c r="B52" s="1">
+        <v>0.158704373261167</v>
       </c>
     </row>
     <row r="53" spans="1:2">
-      <c r="A53" t="s">
+      <c r="A53" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B53">
-        <v>0.1855337238670851</v>
+      <c r="B53" s="1">
+        <v>0.185533723867085</v>
       </c>
     </row>
     <row r="54" spans="1:2">
-      <c r="A54" t="s">
+      <c r="A54" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B54">
-        <v>0.1153907247325953</v>
+      <c r="B54" s="1">
+        <v>0.115390724732595</v>
       </c>
     </row>
     <row r="55" spans="1:2">
-      <c r="A55" t="s">
+      <c r="A55" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="B55">
-        <v>0.1331644074129079</v>
+      <c r="B55" s="1">
+        <v>0.133164407412908</v>
       </c>
     </row>
     <row r="56" spans="1:2">
-      <c r="A56" t="s">
+      <c r="A56" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B56">
-        <v>0.1642528862887344</v>
+      <c r="B56" s="1">
+        <v>0.164252886288734</v>
       </c>
     </row>
     <row r="57" spans="1:2">
-      <c r="A57" t="s">
+      <c r="A57" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="B57">
-        <v>0.1126600402711986</v>
+      <c r="B57" s="1">
+        <v>0.112660040271199</v>
       </c>
     </row>
     <row r="58" spans="1:2">
-      <c r="A58" t="s">
+      <c r="A58" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="B58">
-        <v>0.1443959503692198</v>
+      <c r="B58" s="1">
+        <v>0.14439595036922</v>
       </c>
     </row>
     <row r="59" spans="1:2">
-      <c r="A59" t="s">
+      <c r="A59" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="B59">
-        <v>0.1620486763377602</v>
+      <c r="B59" s="1">
+        <v>0.16204867633776</v>
       </c>
     </row>
     <row r="60" spans="1:2">
-      <c r="A60" t="s">
+      <c r="A60" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="B60">
-        <v>0.1565587526730497</v>
+      <c r="B60" s="1">
+        <v>0.15655875267305</v>
       </c>
     </row>
     <row r="61" spans="1:2">
-      <c r="A61" t="s">
+      <c r="A61" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B61">
+      <c r="B61" s="1">
         <v>0.123555838078093</v>
       </c>
     </row>
     <row r="62" spans="1:2">
-      <c r="A62" t="s">
+      <c r="A62" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="B62">
-        <v>0.1151808784606091</v>
+      <c r="B62" s="1">
+        <v>0.115180878460609</v>
       </c>
     </row>
     <row r="63" spans="1:2">
-      <c r="A63" t="s">
+      <c r="A63" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="B63">
+      <c r="B63" s="1">
         <v>0.128923611856013</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>